--- a/Cleaned_Voter_List.xlsx
+++ b/Cleaned_Voter_List.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G27"/>
+  <dimension ref="A1:G24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -706,53 +706,49 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Rekha Shetty</t>
-        </is>
-      </c>
+      <c r="A10" t="inlineStr"/>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Husbands Name: Sukumar Shetty</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr"/>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>Fathers Name: Raghunath Shetty</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>111</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Female</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr"/>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>BKT2439126</t>
+        </is>
+      </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>REVIEW: Missing ID</t>
+          <t>REVIEW: Missing Name, Missing Age</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Eesha Nak Gaonkar</t>
+          <t>Rekha Shetty</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Fathers Name: Pravin Naik Gaonkar</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>121</t>
-        </is>
-      </c>
+          <t>Husbands Name: Sukumar Shetty</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -770,12 +766,24 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Suzette Miriam Francisca Paula</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr"/>
-      <c r="C12" t="inlineStr"/>
-      <c r="D12" t="inlineStr"/>
+          <t>Eesha Nak Gaonkar</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Fathers Name: Pravin Naik Gaonkar</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>121</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
       <c r="E12" t="inlineStr">
         <is>
           <t>Female</t>
@@ -784,28 +792,24 @@
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>REVIEW: Missing Age, Missing ID</t>
+          <t>REVIEW: Missing ID</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>ouvosesses</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Fathers Name: Julio Gabriel Alvares</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>131</t>
-        </is>
-      </c>
+          <t>Suzette Miriam Francisca Paula</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr"/>
+      <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr"/>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
@@ -816,12 +820,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Crystal Savia Alvares</t>
+          <t>Sovosessaa</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Fathers Name: Julio Gabriel Alvares:</t>
+          <t>Fathers Name: Julio Gabriel Alvares</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -829,42 +833,34 @@
           <t>131</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>Female</t>
-        </is>
-      </c>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
         <is>
-          <t>REVIEW: Missing ID</t>
+          <t>REVIEW: Missing Age, Missing ID</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Sachita Vaigankar</t>
+          <t>Crystal Savia Alvares</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Fathers Name: Sadanand Vaigankar</t>
+          <t>Fathers Name: Julio Gabriel Alvares:</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>132</t>
+          <t>131</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>23</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -882,12 +878,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Parag Sadanand Vaigankar</t>
+          <t>Sachita Vaigankar</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Fathers Name: Sadanand A Vaigankar</t>
+          <t>Fathers Name: Sadanand Vaigankar</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -897,12 +893,12 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>28</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
       <c r="F16" t="inlineStr"/>
@@ -915,22 +911,22 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Mansur Akbaralli Vejee</t>
+          <t>Parag Sadanand Vaigankar</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Fathers Name: Akbarall Habib Vejee</t>
+          <t>Fathers Name: Sadanand A Vaigankar</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>134</t>
+          <t>132</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>23</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -948,12 +944,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Nilofer Mansur Veljee</t>
+          <t>Mansur Akbaralli Vejee</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Husbands Name: Mansur Akbaralli Veljee</t>
+          <t>Fathers Name: Akbarall Habib Vejee</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -961,28 +957,32 @@
           <t>134</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr"/>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>69</t>
+        </is>
+      </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr">
         <is>
-          <t>REVIEW: Missing Age, Missing ID</t>
+          <t>REVIEW: Missing ID</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Zain Mansur Veljee</t>
+          <t>Janesline Perpetual Deonizia</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Fathers Name: Mansur Akbaraili Veljee</t>
+          <t>Husbands Name: Mansur Akbaralli Veljee</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -990,67 +990,71 @@
           <t>134</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
+      <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr">
         <is>
-          <t>REVIEW: Missing ID</t>
+          <t>REVIEW: Missing Age, Missing ID</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Janesline Perpetual Deonizia</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr"/>
+          <t>Brendan Ezekiel Agnelo Vaz</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Fathers Name: Teotone Inas M Vaz</t>
+        </is>
+      </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>151</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
+          <t>134</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr">
         <is>
-          <t>REVIEW: Missing Age, Missing ID</t>
+          <t>REVIEW: Missing ID</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Brendan Ezekiel Agnelo Vaz</t>
+          <t>Sanisha Priokar</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Fathers Name: Teotone Inas M Vaz</t>
+          <t>Fathers Name: Satish Priolkar</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>151</t>
+          <t>161/1</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>32</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1068,27 +1072,27 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Sanisha Priokar</t>
+          <t>Suchitra Kamath</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Fathers Name: Satish Priolkar</t>
+          <t>Husbands Name: Siddartha Kamath</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>161/1</t>
+          <t>163</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>55</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="F22" t="inlineStr"/>
@@ -1101,12 +1105,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Shanavas Hameed</t>
+          <t>Praveen Kamat</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Fathers Name: Mohamed S. Hameed</t>
+          <t>Fathers Name: Shrikrishna Kamat</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1116,12 +1120,12 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>30</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
       <c r="F23" t="inlineStr"/>
@@ -1134,7 +1138,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Shinto Shyam</t>
+          <t>Royston Filomeno Gomes</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1155,85 +1159,6 @@
       </c>
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr">
-        <is>
-          <t>REVIEW: Missing Age, Missing ID</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>Suchitra Kamath</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>Husbands Name: Siddartha Kamath</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>164</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr"/>
-      <c r="F25" t="inlineStr"/>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>REVIEW: Missing ID</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>Praveen Kamat</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>Fathers Name: Shrikrishna Kamat</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>193-A</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr"/>
-      <c r="F26" t="inlineStr"/>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>REVIEW: Missing ID</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>Royston Filomeno Gomes</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr"/>
-      <c r="C27" t="inlineStr"/>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>Male</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr"/>
-      <c r="G27" t="inlineStr">
         <is>
           <t>REVIEW: Missing Age, Missing ID</t>
         </is>
